--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484726_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484726_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.2222</v>
+        <v>7.0587</v>
       </c>
       <c r="E2" t="n">
-        <v>4.2315</v>
+        <v>4.8563</v>
       </c>
       <c r="F2" t="n">
-        <v>1.9907</v>
+        <v>2.2023</v>
       </c>
       <c r="G2" t="n">
         <v>4.9774</v>
@@ -610,13 +610,13 @@
         <v>4.3401</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.1892</v>
+        <v>-0.3527</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.5161</v>
+        <v>-0.8913</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3269</v>
+        <v>0.5385</v>
       </c>
       <c r="V2" t="n">
         <v>0.9244</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.6802</v>
+        <v>4.0506</v>
       </c>
       <c r="E3" t="n">
         <v>1.5561</v>
       </c>
       <c r="F3" t="n">
-        <v>2.1242</v>
+        <v>2.4946</v>
       </c>
       <c r="G3" t="n">
         <v>1.0637</v>
@@ -688,13 +688,13 @@
         <v>2.8305</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.7989000000000001</v>
+        <v>-0.4286</v>
       </c>
       <c r="T3" t="n">
         <v>-0.5726</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2263</v>
+        <v>0.1441</v>
       </c>
       <c r="V3" t="n">
         <v>0.9624</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>G. MEJIA ACOSTA</t>
+          <t>B. MALONE NAVARRO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.1573</v>
+        <v>1.2477</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.8064</v>
+        <v>-0.0832</v>
       </c>
       <c r="F4" t="n">
-        <v>2.9637</v>
+        <v>1.3309</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.8581</v>
+        <v>0.1413</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.9706</v>
+        <v>-0.2896</v>
       </c>
       <c r="I4" t="n">
-        <v>1.1125</v>
+        <v>0.4309</v>
       </c>
       <c r="J4" t="n">
-        <v>0.2916</v>
+        <v>0.1257</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.4743</v>
+        <v>0.08450000000000001</v>
       </c>
       <c r="L4" t="n">
-        <v>0.7659</v>
+        <v>0.0411</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.1497</v>
+        <v>0.0157</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.4963</v>
+        <v>-0.3741</v>
       </c>
       <c r="O4" t="n">
-        <v>0.3466</v>
+        <v>0.3897</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.7548</v>
+        <v>0.1887</v>
       </c>
       <c r="Q4" t="n">
-        <v>-4.1514</v>
+        <v>-0.1887</v>
       </c>
       <c r="R4" t="n">
-        <v>3.3966</v>
+        <v>0.3774</v>
       </c>
       <c r="S4" t="n">
-        <v>1.2797</v>
+        <v>0.2762</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.0407</v>
+        <v>-0.0201</v>
       </c>
       <c r="U4" t="n">
-        <v>1.3204</v>
+        <v>0.2963</v>
       </c>
       <c r="V4" t="n">
-        <v>2.4904</v>
+        <v>0.6415999999999999</v>
       </c>
       <c r="W4" t="n">
-        <v>3.094</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.6036</v>
+        <v>0.6415999999999999</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>B. MALONE NAVARRO</t>
+          <t>G. MEJIA ACOSTA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.0709</v>
+        <v>0.9927</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.1806</v>
+        <v>-1.4683</v>
       </c>
       <c r="F5" t="n">
-        <v>1.2516</v>
+        <v>2.461</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1413</v>
+        <v>-0.8581</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.2896</v>
+        <v>-1.9706</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4309</v>
+        <v>1.1125</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1257</v>
+        <v>0.2916</v>
       </c>
       <c r="K5" t="n">
-        <v>0.08450000000000001</v>
+        <v>-0.4743</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0411</v>
+        <v>0.7659</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0157</v>
+        <v>-1.1497</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.3741</v>
+        <v>-1.4963</v>
       </c>
       <c r="O5" t="n">
-        <v>0.3897</v>
+        <v>0.3466</v>
       </c>
       <c r="P5" t="n">
-        <v>0.1887</v>
+        <v>-0.7548</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.1887</v>
+        <v>-4.1514</v>
       </c>
       <c r="R5" t="n">
-        <v>0.3774</v>
+        <v>3.3966</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0994</v>
+        <v>0.1152</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1176</v>
+        <v>-0.7026</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2169</v>
+        <v>0.8178</v>
       </c>
       <c r="V5" t="n">
-        <v>0.6415999999999999</v>
+        <v>2.4904</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>3.094</v>
       </c>
       <c r="X5" t="n">
-        <v>0.6415999999999999</v>
+        <v>-0.6036</v>
       </c>
     </row>
     <row r="6">
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>T. BOUNDI</t>
+          <t>A. CABALLERO ROMERO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0395</v>
+        <v>-0.1585</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1521</v>
+        <v>-0.3764</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.1126</v>
+        <v>0.2179</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.2804</v>
+        <v>-0.4343</v>
       </c>
       <c r="H7" t="n">
-        <v>0.3929</v>
+        <v>-0.4343</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.6733</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>1.2488</v>
+        <v>0.0211</v>
       </c>
       <c r="K7" t="n">
-        <v>1.1254</v>
+        <v>0.0211</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1234</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.5292</v>
+        <v>-0.4555</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.7325</v>
+        <v>-0.4555</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.7967</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>0.1887</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.887</v>
+        <v>-0.3774</v>
       </c>
       <c r="R7" t="n">
-        <v>2.0757</v>
+        <v>0.3774</v>
       </c>
       <c r="S7" t="n">
-        <v>1.452</v>
+        <v>-0.3658</v>
       </c>
       <c r="T7" t="n">
-        <v>1.4319</v>
+        <v>-0.0201</v>
       </c>
       <c r="U7" t="n">
-        <v>0.02</v>
+        <v>-0.3456</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.3208</v>
+        <v>0.6415999999999999</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.6415999999999999</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0.3208</v>
+        <v>0.6415999999999999</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. CABALLERO ROMERO</t>
+          <t>D. SALVADOR ESCUDER</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.2824</v>
+        <v>-0.5135999999999999</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.4738</v>
+        <v>-0.1654</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1914</v>
+        <v>-0.3482</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.4343</v>
+        <v>-1.8016</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.4343</v>
+        <v>-0.1409</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>-1.6608</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0211</v>
+        <v>-0.4622</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0211</v>
+        <v>1.4368</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>-1.899</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.4555</v>
+        <v>-1.3394</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.4555</v>
+        <v>-1.5777</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>0.2383</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1.3209</v>
       </c>
       <c r="Q8" t="n">
         <v>-0.3774</v>
       </c>
       <c r="R8" t="n">
-        <v>0.3774</v>
+        <v>1.6983</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.4897</v>
+        <v>-0.6744</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1176</v>
+        <v>-0.571</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.3721</v>
+        <v>-0.1034</v>
       </c>
       <c r="V8" t="n">
         <v>0.6415999999999999</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.2452</v>
       </c>
       <c r="X8" t="n">
-        <v>0.6415999999999999</v>
+        <v>-0.6036</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>C. GONZALEZ DIAZ</t>
+          <t>T. BOUNDI</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.6627999999999999</v>
+        <v>-0.9315</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.8551</v>
+        <v>-0.6072</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1923</v>
+        <v>-0.3243</v>
       </c>
       <c r="G9" t="n">
-        <v>-3.1756</v>
+        <v>-1.2804</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.1389</v>
+        <v>0.3929</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.0368</v>
+        <v>-1.6733</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.9661</v>
+        <v>1.2488</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.7476</v>
+        <v>1.1254</v>
       </c>
       <c r="L9" t="n">
-        <v>0.7815</v>
+        <v>0.1234</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.2095</v>
+        <v>-2.5292</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.3913</v>
+        <v>-0.7325</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.8182</v>
+        <v>-1.7967</v>
       </c>
       <c r="P9" t="n">
-        <v>3.3966</v>
+        <v>0.1887</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.1887</v>
+        <v>-1.887</v>
       </c>
       <c r="R9" t="n">
-        <v>3.5853</v>
+        <v>2.0757</v>
       </c>
       <c r="S9" t="n">
-        <v>0.9841</v>
+        <v>0.481</v>
       </c>
       <c r="T9" t="n">
-        <v>0.2997</v>
+        <v>0.6726</v>
       </c>
       <c r="U9" t="n">
-        <v>0.6843</v>
+        <v>-0.1916</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.8678</v>
+        <v>-0.3208</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>-0.6415999999999999</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.8678</v>
+        <v>0.3208</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>D. SALVADOR ESCUDER</t>
+          <t>C. GONZALEZ DIAZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.1595</v>
+        <v>-1.1696</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.6526</v>
+        <v>-0.9122</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.5069</v>
+        <v>-0.2574</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.8016</v>
+        <v>-3.1756</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.1409</v>
+        <v>-2.1389</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.6608</v>
+        <v>-1.0368</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.4622</v>
+        <v>-0.9661</v>
       </c>
       <c r="K10" t="n">
-        <v>1.4368</v>
+        <v>-1.7476</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.899</v>
+        <v>0.7815</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.3394</v>
+        <v>-2.2095</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.5777</v>
+        <v>-0.3913</v>
       </c>
       <c r="O10" t="n">
-        <v>0.2383</v>
+        <v>-1.8182</v>
       </c>
       <c r="P10" t="n">
-        <v>1.3209</v>
+        <v>3.3966</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.3774</v>
+        <v>-0.1887</v>
       </c>
       <c r="R10" t="n">
-        <v>1.6983</v>
+        <v>3.5853</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.3203</v>
+        <v>0.4772</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.0582</v>
+        <v>0.2426</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2621</v>
+        <v>0.2346</v>
       </c>
       <c r="V10" t="n">
-        <v>0.6415999999999999</v>
+        <v>-1.8678</v>
       </c>
       <c r="W10" t="n">
-        <v>1.2452</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.6036</v>
+        <v>-1.8678</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.312</v>
+        <v>-1.6788</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.0774</v>
+        <v>-0.5499000000000001</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.2346</v>
+        <v>-1.1288</v>
       </c>
       <c r="G11" t="n">
         <v>-2.9495</v>
@@ -1312,13 +1312,13 @@
         <v>3.5853</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.6836</v>
+        <v>-1.0504</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.5161</v>
+        <v>-0.9887</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1675</v>
+        <v>-0.0617</v>
       </c>
       <c r="V11" t="n">
         <v>-1.2642</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.6179</v>
+        <v>-4.5865</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.8996</v>
+        <v>-5.0799</v>
       </c>
       <c r="F12" t="n">
-        <v>0.2817</v>
+        <v>0.4934</v>
       </c>
       <c r="G12" t="n">
         <v>-3.2293</v>
@@ -1390,13 +1390,13 @@
         <v>4.1514</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.8606</v>
+        <v>-0.8292</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.5285</v>
+        <v>-0.7087</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.3321</v>
+        <v>-0.1205</v>
       </c>
       <c r="V12" t="n">
         <v>-0.9054</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.752500000000002</v>
+        <v>4.928200000000003</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.388800000000001</v>
+        <v>-2.2131</v>
       </c>
       <c r="F13" t="n">
-        <v>7.141500000000002</v>
+        <v>7.141400000000003</v>
       </c>
       <c r="G13" t="n">
         <v>-6.929399999999999</v>
@@ -1447,7 +1447,7 @@
         <v>6.19</v>
       </c>
       <c r="L13" t="n">
-        <v>3.4609</v>
+        <v>3.460900000000001</v>
       </c>
       <c r="M13" t="n">
         <v>-16.5804</v>
@@ -1468,13 +1468,13 @@
         <v>26.418</v>
       </c>
       <c r="S13" t="n">
-        <v>-3.5271</v>
+        <v>-2.3515</v>
       </c>
       <c r="T13" t="n">
-        <v>-4.7358</v>
+        <v>-3.5599</v>
       </c>
       <c r="U13" t="n">
-        <v>1.2084</v>
+        <v>1.2085</v>
       </c>
       <c r="V13" t="n">
         <v>1.943800000000001</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>9.1652</v>
+        <v>8.1188</v>
       </c>
       <c r="E14" t="n">
-        <v>6.3889</v>
+        <v>5.6094</v>
       </c>
       <c r="F14" t="n">
-        <v>2.7763</v>
+        <v>2.5094</v>
       </c>
       <c r="G14" t="n">
         <v>5.3421</v>
@@ -1546,13 +1546,13 @@
         <v>2.4531</v>
       </c>
       <c r="S14" t="n">
-        <v>2.7859</v>
+        <v>1.7395</v>
       </c>
       <c r="T14" t="n">
-        <v>1.2679</v>
+        <v>0.4884</v>
       </c>
       <c r="U14" t="n">
-        <v>1.518</v>
+        <v>1.2511</v>
       </c>
       <c r="V14" t="n">
         <v>4.0564</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>E. RHAIEM SANCHEZ</t>
+          <t>L. CARRIÓN GALINDO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.0315</v>
+        <v>0.9509</v>
       </c>
       <c r="E15" t="n">
-        <v>0.706</v>
+        <v>0.9509</v>
       </c>
       <c r="F15" t="n">
-        <v>0.3255</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.378</v>
+        <v>0.9509</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.0665</v>
+        <v>0.9509</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.3115</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>0.6192</v>
+        <v>0.9509</v>
       </c>
       <c r="K15" t="n">
-        <v>0.4547</v>
+        <v>0.9509</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1645</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.9972</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.5212</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.476</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.9435</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.0757</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.1322</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>0.806</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>0.6153999999999999</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1905</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>1.547</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.547</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>L. CARRIÓN GALINDO</t>
+          <t>C. TEASLEY JR</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9509</v>
+        <v>0.7783</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9509</v>
+        <v>0.5108</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>0.2676</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9509</v>
+        <v>2.4385</v>
       </c>
       <c r="H16" t="n">
-        <v>0.9509</v>
+        <v>-0.3302</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>2.7688</v>
       </c>
       <c r="J16" t="n">
-        <v>0.9509</v>
+        <v>4.807</v>
       </c>
       <c r="K16" t="n">
-        <v>0.9509</v>
+        <v>0.9563</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>3.8507</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>-2.3684</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>-1.2865</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>-1.0819</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>-1.3209</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-3.5853</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>2.2644</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>-0.0185</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>-0.3901</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>0.3716</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>-0.3208</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>-0.3208</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>R. DIAZ GALIAN</t>
+          <t>E. RHAIEM SANCHEZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3074</v>
+        <v>0.7043</v>
       </c>
       <c r="E17" t="n">
-        <v>0.4971</v>
+        <v>0.5111</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.1897</v>
+        <v>0.1933</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.1176</v>
+        <v>-0.378</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.1025</v>
+        <v>-0.0665</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.015</v>
+        <v>-0.3115</v>
       </c>
       <c r="J17" t="n">
-        <v>1.085</v>
+        <v>0.6192</v>
       </c>
       <c r="K17" t="n">
-        <v>0.3858</v>
+        <v>0.4547</v>
       </c>
       <c r="L17" t="n">
-        <v>0.6992</v>
+        <v>0.1645</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.2026</v>
+        <v>-0.9972</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.4883</v>
+        <v>-0.5212</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.7143</v>
+        <v>-0.476</v>
       </c>
       <c r="P17" t="n">
-        <v>0.7548</v>
+        <v>-0.9435</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-2.0757</v>
       </c>
       <c r="R17" t="n">
-        <v>0.7548</v>
+        <v>1.1322</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.3298</v>
+        <v>0.4788</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.5879</v>
+        <v>0.4206</v>
       </c>
       <c r="U17" t="n">
-        <v>0.2581</v>
+        <v>0.0582</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.547</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.547</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>C. TEASLEY JR</t>
+          <t>R. DIAZ GALIAN</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.547</v>
+        <v>0.4578</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.0738</v>
+        <v>0.5946</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4732</v>
+        <v>-0.1368</v>
       </c>
       <c r="G18" t="n">
-        <v>2.4385</v>
+        <v>-0.1176</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.3302</v>
+        <v>-0.1025</v>
       </c>
       <c r="I18" t="n">
-        <v>2.7688</v>
+        <v>-0.015</v>
       </c>
       <c r="J18" t="n">
-        <v>4.807</v>
+        <v>1.085</v>
       </c>
       <c r="K18" t="n">
-        <v>0.9563</v>
+        <v>0.3858</v>
       </c>
       <c r="L18" t="n">
-        <v>3.8507</v>
+        <v>0.6992</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.3684</v>
+        <v>-1.2026</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.2865</v>
+        <v>-0.4883</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.0819</v>
+        <v>-0.7143</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.3209</v>
+        <v>0.7548</v>
       </c>
       <c r="Q18" t="n">
-        <v>-3.5853</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>2.2644</v>
+        <v>0.7548</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.3438</v>
+        <v>-0.1794</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.9747</v>
+        <v>-0.4904</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.3691</v>
+        <v>0.311</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.3208</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.3208</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.9485</v>
+        <v>-0.6947</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.3307</v>
+        <v>-1.2333</v>
       </c>
       <c r="F19" t="n">
-        <v>0.3822</v>
+        <v>0.5386</v>
       </c>
       <c r="G19" t="n">
         <v>-0.8676</v>
@@ -1936,13 +1936,13 @@
         <v>0.9435</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.0999</v>
+        <v>0.1539</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.5044</v>
+        <v>-0.407</v>
       </c>
       <c r="U19" t="n">
-        <v>0.4045</v>
+        <v>0.5608</v>
       </c>
       <c r="V19" t="n">
         <v>-0.9244</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.1251</v>
+        <v>-1.2527</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.342</v>
+        <v>-2.7318</v>
       </c>
       <c r="F20" t="n">
-        <v>1.2169</v>
+        <v>1.4791</v>
       </c>
       <c r="G20" t="n">
         <v>1.3196</v>
@@ -2014,13 +2014,13 @@
         <v>2.4531</v>
       </c>
       <c r="S20" t="n">
-        <v>0.7254</v>
+        <v>0.5979</v>
       </c>
       <c r="T20" t="n">
-        <v>0.4173</v>
+        <v>0.0276</v>
       </c>
       <c r="U20" t="n">
-        <v>0.3081</v>
+        <v>0.5703</v>
       </c>
       <c r="V20" t="n">
         <v>-1.2832</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.9856</v>
+        <v>-2.6608</v>
       </c>
       <c r="E21" t="n">
-        <v>-4.3698</v>
+        <v>-4.1749</v>
       </c>
       <c r="F21" t="n">
-        <v>1.3842</v>
+        <v>1.5141</v>
       </c>
       <c r="G21" t="n">
         <v>-1.3719</v>
@@ -2092,13 +2092,13 @@
         <v>0.9435</v>
       </c>
       <c r="S21" t="n">
-        <v>0.3868</v>
+        <v>0.7116</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.4456</v>
+        <v>-0.2508</v>
       </c>
       <c r="U21" t="n">
-        <v>0.8325</v>
+        <v>0.9624</v>
       </c>
       <c r="V21" t="n">
         <v>0.2639</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.9813</v>
+        <v>-3.5049</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.0804</v>
+        <v>-2.4958</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.9009</v>
+        <v>-1.0091</v>
       </c>
       <c r="G22" t="n">
         <v>0.1664</v>
@@ -2170,13 +2170,13 @@
         <v>2.0757</v>
       </c>
       <c r="S22" t="n">
-        <v>0.1541</v>
+        <v>0.6304999999999999</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.8818</v>
+        <v>-0.2972</v>
       </c>
       <c r="U22" t="n">
-        <v>1.0359</v>
+        <v>0.9277</v>
       </c>
       <c r="V22" t="n">
         <v>-2.7922</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.6199</v>
+        <v>-5.9999</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.4876</v>
+        <v>-4.6824</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.1323</v>
+        <v>-1.3175</v>
       </c>
       <c r="G23" t="n">
         <v>-0.5528999999999999</v>
@@ -2248,13 +2248,13 @@
         <v>1.1322</v>
       </c>
       <c r="S23" t="n">
-        <v>0.4426</v>
+        <v>0.0626</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.1147</v>
+        <v>-0.3095</v>
       </c>
       <c r="U23" t="n">
-        <v>0.5573</v>
+        <v>0.3721</v>
       </c>
       <c r="V23" t="n">
         <v>-2.4904</v>
@@ -2281,16 +2281,16 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.7524</v>
+        <v>-3.1029</v>
       </c>
       <c r="E24" t="n">
-        <v>-7.141400000000001</v>
+        <v>-7.1414</v>
       </c>
       <c r="F24" t="n">
-        <v>3.389</v>
+        <v>4.0387</v>
       </c>
       <c r="G24" t="n">
-        <v>6.9295</v>
+        <v>6.929500000000001</v>
       </c>
       <c r="H24" t="n">
         <v>4.547</v>
@@ -2326,19 +2326,19 @@
         <v>14.1525</v>
       </c>
       <c r="S24" t="n">
-        <v>3.5273</v>
+        <v>4.1769</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.2085</v>
+        <v>-1.2084</v>
       </c>
       <c r="U24" t="n">
-        <v>4.735799999999999</v>
+        <v>5.385199999999999</v>
       </c>
       <c r="V24" t="n">
-        <v>-1.9437</v>
+        <v>-1.943699999999999</v>
       </c>
       <c r="W24" t="n">
-        <v>3.904500000000001</v>
+        <v>3.9045</v>
       </c>
       <c r="X24" t="n">
         <v>-5.8482</v>
